--- a/fact_abastecimiento_logistica/outputs/06_historial_entrenamiento.xlsx
+++ b/fact_abastecimiento_logistica/outputs/06_historial_entrenamiento.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -618,7 +618,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1.11065161615208</v>
+        <v>1.110651616152079</v>
       </c>
       <c r="C12" t="n">
         <v>1.106292599349206</v>
@@ -876,7 +876,7 @@
         <v>1.058648733486778</v>
       </c>
       <c r="C27" t="n">
-        <v>1.054414846454483</v>
+        <v>1.054414846454482</v>
       </c>
       <c r="D27" t="n">
         <v>0.5105099260412612</v>
@@ -1111,7 +1111,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1.007200345165668</v>
+        <v>1.007200345165669</v>
       </c>
       <c r="C41" t="n">
         <v>1.002725349639281</v>
@@ -1145,10 +1145,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.9997410354745303</v>
+        <v>0.9997410354745301</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9952540444707313</v>
+        <v>0.9952540444707312</v>
       </c>
       <c r="D43" t="n">
         <v>0.5989684702218763</v>
@@ -1182,7 +1182,7 @@
         <v>0.9922554743274822</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9877573762853077</v>
+        <v>0.9877573762853075</v>
       </c>
       <c r="D45" t="n">
         <v>0.6161930712339432</v>
@@ -1213,7 +1213,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.984736269721177</v>
+        <v>0.9847362697211771</v>
       </c>
       <c r="C47" t="n">
         <v>0.9802291803858035</v>
@@ -1264,7 +1264,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.9733810722848721</v>
+        <v>0.973381072284872</v>
       </c>
       <c r="C50" t="n">
         <v>0.9688689047390169</v>
@@ -1366,7 +1366,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>0.9503700079813813</v>
+        <v>0.9503700079813815</v>
       </c>
       <c r="C56" t="n">
         <v>0.945902282287198</v>
@@ -1417,7 +1417,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>0.9387308587428241</v>
+        <v>0.938730858742824</v>
       </c>
       <c r="C59" t="n">
         <v>0.9343214880320373</v>
@@ -1437,7 +1437,7 @@
         <v>0.9348363910806802</v>
       </c>
       <c r="C60" t="n">
-        <v>0.930452355643883</v>
+        <v>0.9304523556438827</v>
       </c>
       <c r="D60" t="n">
         <v>0.7057220708446866</v>
@@ -1485,7 +1485,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>0.9231237499537017</v>
+        <v>0.9231237499537019</v>
       </c>
       <c r="C63" t="n">
         <v>0.9188335400758413</v>
@@ -1573,7 +1573,7 @@
         <v>0.903578606842718</v>
       </c>
       <c r="C68" t="n">
-        <v>0.899502455192417</v>
+        <v>0.8995024551924168</v>
       </c>
       <c r="D68" t="n">
         <v>0.717983651226158</v>
@@ -1604,10 +1604,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>0.8957819791495484</v>
+        <v>0.8957819791495485</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8918103661162049</v>
+        <v>0.891810366116205</v>
       </c>
       <c r="D70" t="n">
         <v>0.7184702218762165</v>
@@ -1621,7 +1621,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>0.8918933976690614</v>
+        <v>0.8918933976690613</v>
       </c>
       <c r="C71" t="n">
         <v>0.8879778093221274</v>
@@ -1638,7 +1638,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>0.8880129864102931</v>
+        <v>0.888012986410293</v>
       </c>
       <c r="C72" t="n">
         <v>0.8841558093304661</v>
@@ -1675,7 +1675,7 @@
         <v>0.8802816198522104</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8765480431818586</v>
+        <v>0.8765480431818585</v>
       </c>
       <c r="D74" t="n">
         <v>0.7211950175165434</v>
@@ -1743,7 +1743,7 @@
         <v>0.8649702861878896</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8615080940073903</v>
+        <v>0.8615080940073901</v>
       </c>
       <c r="D78" t="n">
         <v>0.7250875827170105</v>
@@ -1791,7 +1791,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>0.8536556037904571</v>
+        <v>0.8536556037904574</v>
       </c>
       <c r="C81" t="n">
         <v>0.8504145157175962</v>
@@ -1859,7 +1859,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>0.8388509836332582</v>
+        <v>0.8388509836332584</v>
       </c>
       <c r="C85" t="n">
         <v>0.8359218172155946</v>
@@ -1879,7 +1879,7 @@
         <v>0.8352071592982411</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8323581874309844</v>
+        <v>0.8323581874309842</v>
       </c>
       <c r="D86" t="n">
         <v>0.7289801479174777</v>
@@ -1944,7 +1944,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>0.8208912129517093</v>
+        <v>0.8208912129517091</v>
       </c>
       <c r="C90" t="n">
         <v>0.8183681915051735</v>
@@ -1961,7 +1961,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>0.817381746688858</v>
+        <v>0.8173817466888582</v>
       </c>
       <c r="C91" t="n">
         <v>0.8149409356353629</v>
@@ -1995,7 +1995,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>0.8104522986358377</v>
+        <v>0.8104522986358378</v>
       </c>
       <c r="C93" t="n">
         <v>0.8081760557754022</v>
@@ -2012,7 +2012,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>0.807033875981701</v>
+        <v>0.8070338759817012</v>
       </c>
       <c r="C94" t="n">
         <v>0.8048398124131863</v>
@@ -2029,7 +2029,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>0.8036472768449285</v>
+        <v>0.8036472768449284</v>
       </c>
       <c r="C95" t="n">
         <v>0.8015352161351288</v>
@@ -2046,7 +2046,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>0.8002931507874275</v>
+        <v>0.8002931507874276</v>
       </c>
       <c r="C96" t="n">
         <v>0.798262845938473</v>
@@ -2114,7 +2114,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>0.7872123383457301</v>
+        <v>0.7872123383457299</v>
       </c>
       <c r="C100" t="n">
         <v>0.7855054173915083</v>
@@ -2148,7 +2148,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>0.7808793303616355</v>
+        <v>0.7808793303616354</v>
       </c>
       <c r="C102" t="n">
         <v>0.7793312623727895</v>
@@ -2182,7 +2182,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>0.7746876783317875</v>
+        <v>0.7746876783317876</v>
       </c>
       <c r="C104" t="n">
         <v>0.7732961775947916</v>
@@ -2199,7 +2199,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>0.7716452453728806</v>
+        <v>0.7716452453728807</v>
       </c>
       <c r="C105" t="n">
         <v>0.7703310963469385</v>
@@ -2216,7 +2216,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>0.7686384967038774</v>
+        <v>0.7686384967038775</v>
       </c>
       <c r="C106" t="n">
         <v>0.7674010423340227</v>
@@ -2233,7 +2233,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>0.7656674297529495</v>
+        <v>0.7656674297529497</v>
       </c>
       <c r="C107" t="n">
         <v>0.7645059881817847</v>
@@ -2253,7 +2253,7 @@
         <v>0.7627319894910435</v>
       </c>
       <c r="C108" t="n">
-        <v>0.7616458555078213</v>
+        <v>0.7616458555078212</v>
       </c>
       <c r="D108" t="n">
         <v>0.7434799532892176</v>
@@ -2352,7 +2352,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>0.7458586081984871</v>
+        <v>0.745858608198487</v>
       </c>
       <c r="C114" t="n">
         <v>0.7452083901138116</v>
@@ -2372,7 +2372,7 @@
         <v>0.7431672844397208</v>
       </c>
       <c r="C115" t="n">
-        <v>0.7425869127559128</v>
+        <v>0.7425869127559127</v>
       </c>
       <c r="D115" t="n">
         <v>0.7458154924094978</v>
@@ -2386,7 +2386,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>0.7405096579197749</v>
+        <v>0.7405096579197747</v>
       </c>
       <c r="C116" t="n">
         <v>0.7399982991164892</v>
@@ -2423,7 +2423,7 @@
         <v>0.7352939913738262</v>
       </c>
       <c r="C118" t="n">
-        <v>0.7349181311647962</v>
+        <v>0.7349181311647961</v>
       </c>
       <c r="D118" t="n">
         <v>0.7463020630595563</v>
@@ -2522,7 +2522,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>0.7204142483463792</v>
+        <v>0.7204142483463793</v>
       </c>
       <c r="C124" t="n">
         <v>0.7204245650783138</v>
@@ -2556,7 +2556,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>0.7156986791728662</v>
+        <v>0.7156986791728663</v>
       </c>
       <c r="C126" t="n">
         <v>0.7158310501365583</v>
@@ -2627,7 +2627,7 @@
         <v>0.7066133304548137</v>
       </c>
       <c r="C130" t="n">
-        <v>0.7069802423217744</v>
+        <v>0.7069802423217743</v>
       </c>
       <c r="D130" t="n">
         <v>0.7511677695601401</v>
@@ -2709,10 +2709,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>0.6958706045865458</v>
+        <v>0.6958706045865457</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6965138653011455</v>
+        <v>0.6965138653011453</v>
       </c>
       <c r="D135" t="n">
         <v>0.7513623978201635</v>
@@ -2814,7 +2814,7 @@
         <v>0.6838154953354438</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6847682522069649</v>
+        <v>0.684768252206965</v>
       </c>
       <c r="D141" t="n">
         <v>0.752724795640327</v>
@@ -2828,10 +2828,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>0.6818899455099626</v>
+        <v>0.6818899455099627</v>
       </c>
       <c r="C142" t="n">
-        <v>0.6828921639968762</v>
+        <v>0.6828921639968764</v>
       </c>
       <c r="D142" t="n">
         <v>0.7535033086804204</v>
@@ -2967,7 +2967,7 @@
         <v>0.6672875677080282</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6686664055854653</v>
+        <v>0.6686664055854652</v>
       </c>
       <c r="D150" t="n">
         <v>0.7555469054106656</v>
@@ -2998,7 +2998,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>0.6638489868315075</v>
+        <v>0.6638489868315076</v>
       </c>
       <c r="C152" t="n">
         <v>0.6653171835581777</v>
@@ -3015,7 +3015,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>0.6621599886095291</v>
+        <v>0.6621599886095292</v>
       </c>
       <c r="C153" t="n">
         <v>0.6636722132362334</v>
@@ -3052,7 +3052,7 @@
         <v>0.6588412989615055</v>
       </c>
       <c r="C155" t="n">
-        <v>0.6604403303937229</v>
+        <v>0.660440330393723</v>
       </c>
       <c r="D155" t="n">
         <v>0.7567146749708058</v>
@@ -3069,7 +3069,7 @@
         <v>0.657211112186661</v>
       </c>
       <c r="C156" t="n">
-        <v>0.6588529427880814</v>
+        <v>0.6588529427880815</v>
       </c>
       <c r="D156" t="n">
         <v>0.7569093032308292</v>
@@ -3086,7 +3086,7 @@
         <v>0.6556000420830959</v>
       </c>
       <c r="C157" t="n">
-        <v>0.657284281828406</v>
+        <v>0.6572842818284059</v>
       </c>
       <c r="D157" t="n">
         <v>0.7569093032308292</v>
@@ -3219,7 +3219,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>0.6433722678348643</v>
+        <v>0.6433722678348645</v>
       </c>
       <c r="C165" t="n">
         <v>0.6453827612960492</v>
@@ -3270,7 +3270,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>0.6390754414732126</v>
+        <v>0.6390754414732125</v>
       </c>
       <c r="C168" t="n">
         <v>0.6412028144050089</v>
@@ -3341,7 +3341,7 @@
         <v>0.6335769566612786</v>
       </c>
       <c r="C172" t="n">
-        <v>0.6358560053490798</v>
+        <v>0.6358560053490799</v>
       </c>
       <c r="D172" t="n">
         <v>0.7555469054106656</v>
@@ -3355,7 +3355,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>0.6322422327216302</v>
+        <v>0.6322422327216303</v>
       </c>
       <c r="C173" t="n">
         <v>0.634558497486617</v>
@@ -3389,7 +3389,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>0.6296193543107431</v>
+        <v>0.629619354310743</v>
       </c>
       <c r="C175" t="n">
         <v>0.6320092472805502</v>
@@ -3406,7 +3406,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>0.6283308352036889</v>
+        <v>0.6283308352036888</v>
       </c>
       <c r="C176" t="n">
         <v>0.6307571507011451</v>
@@ -3491,7 +3491,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>0.6221103366075509</v>
+        <v>0.622110336607551</v>
       </c>
       <c r="C181" t="n">
         <v>0.6247150310609597</v>
@@ -3508,7 +3508,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>0.620909444995708</v>
+        <v>0.6209094449957081</v>
       </c>
       <c r="C182" t="n">
         <v>0.6235490948991197</v>
@@ -3542,7 +3542,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>0.618549520877509</v>
+        <v>0.6185495208775089</v>
       </c>
       <c r="C184" t="n">
         <v>0.6212583841239081</v>
@@ -3562,7 +3562,7 @@
         <v>0.6173901597009099</v>
       </c>
       <c r="C185" t="n">
-        <v>0.6201332844667375</v>
+        <v>0.6201332844667374</v>
       </c>
       <c r="D185" t="n">
         <v>0.7567146749708058</v>
@@ -3593,7 +3593,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>0.6151118312659239</v>
+        <v>0.6151118312659241</v>
       </c>
       <c r="C187" t="n">
         <v>0.6179227940819706</v>
@@ -3610,7 +3610,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>0.6139925462697394</v>
+        <v>0.6139925462697395</v>
       </c>
       <c r="C188" t="n">
         <v>0.6168370862030025</v>
@@ -3627,7 +3627,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>0.6128863051853197</v>
+        <v>0.6128863051853198</v>
       </c>
       <c r="C189" t="n">
         <v>0.6157641938270311</v>
@@ -3661,7 +3661,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>0.6107123382656066</v>
+        <v>0.6107123382656067</v>
       </c>
       <c r="C191" t="n">
         <v>0.6136562346368095</v>
@@ -3678,7 +3678,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>0.6096443083140344</v>
+        <v>0.6096443083140345</v>
       </c>
       <c r="C192" t="n">
         <v>0.6126208602516143</v>
@@ -3746,10 +3746,10 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>0.6054950709321255</v>
+        <v>0.6054950709321256</v>
       </c>
       <c r="C196" t="n">
-        <v>0.6085998619512859</v>
+        <v>0.608599861951286</v>
       </c>
       <c r="D196" t="n">
         <v>0.7569093032308292</v>
@@ -3834,7 +3834,7 @@
         <v>0.6005741747572332</v>
       </c>
       <c r="C201" t="n">
-        <v>0.6038336249577755</v>
+        <v>0.6038336249577756</v>
       </c>
       <c r="D201" t="n">
         <v>0.7576878162709225</v>
@@ -3865,10 +3865,10 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>0.598684861073257</v>
+        <v>0.5986848610732571</v>
       </c>
       <c r="C203" t="n">
-        <v>0.602004306910541</v>
+        <v>0.6020043069105411</v>
       </c>
       <c r="D203" t="n">
         <v>0.7577851304009342</v>
@@ -3882,7 +3882,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>0.5977565965593827</v>
+        <v>0.5977565965593826</v>
       </c>
       <c r="C204" t="n">
         <v>0.6011056208277853</v>
@@ -3933,10 +3933,10 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>0.5950357751098428</v>
+        <v>0.595035775109843</v>
       </c>
       <c r="C207" t="n">
-        <v>0.5984718006950555</v>
+        <v>0.5984718006950553</v>
       </c>
       <c r="D207" t="n">
         <v>0.7577851304009342</v>
@@ -4106,7 +4106,7 @@
         <v>0.5866204547313502</v>
       </c>
       <c r="C217" t="n">
-        <v>0.590326509993369</v>
+        <v>0.5903265099933691</v>
       </c>
       <c r="D217" t="n">
         <v>0.7592448423511093</v>
@@ -4137,7 +4137,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>0.5850507235924017</v>
+        <v>0.5850507235924016</v>
       </c>
       <c r="C219" t="n">
         <v>0.5888069329746358</v>
@@ -4171,7 +4171,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>0.5835165566723028</v>
+        <v>0.583516556672303</v>
       </c>
       <c r="C221" t="n">
         <v>0.5873216134661623</v>
@@ -4188,7 +4188,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>0.5827625249716972</v>
+        <v>0.5827625249716973</v>
       </c>
       <c r="C222" t="n">
         <v>0.5865915159663957</v>
@@ -4222,7 +4222,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>0.5812800066223215</v>
+        <v>0.5812800066223214</v>
       </c>
       <c r="C224" t="n">
         <v>0.5851558912700664</v>
@@ -4290,7 +4290,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>0.5784141045038907</v>
+        <v>0.5784141045038909</v>
       </c>
       <c r="C228" t="n">
         <v>0.582379923291938</v>
@@ -4307,7 +4307,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>0.5777176628237525</v>
+        <v>0.5777176628237524</v>
       </c>
       <c r="C229" t="n">
         <v>0.5817051757286701</v>
@@ -4324,7 +4324,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>0.5770290276788751</v>
+        <v>0.5770290276788752</v>
       </c>
       <c r="C230" t="n">
         <v>0.5810379246945294</v>
@@ -4426,10 +4426,10 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>0.5730555808514894</v>
+        <v>0.5730555808514893</v>
       </c>
       <c r="C236" t="n">
-        <v>0.5771864764725886</v>
+        <v>0.5771864764725885</v>
       </c>
       <c r="D236" t="n">
         <v>0.7603152977812379</v>
@@ -4477,7 +4477,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>0.5711663478066188</v>
+        <v>0.571166347806619</v>
       </c>
       <c r="C239" t="n">
         <v>0.5753543783002256</v>
@@ -4497,7 +4497,7 @@
         <v>0.5705504311483409</v>
       </c>
       <c r="C240" t="n">
-        <v>0.5747569652281913</v>
+        <v>0.5747569652281914</v>
       </c>
       <c r="D240" t="n">
         <v>0.7603152977812379</v>
@@ -4528,7 +4528,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>0.5693388086659352</v>
+        <v>0.5693388086659353</v>
       </c>
       <c r="C242" t="n">
         <v>0.5735815681729801</v>
@@ -4545,7 +4545,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>0.5687429303266215</v>
+        <v>0.5687429303266214</v>
       </c>
       <c r="C243" t="n">
         <v>0.5730034220907784</v>
@@ -4565,7 +4565,7 @@
         <v>0.5681535609626561</v>
       </c>
       <c r="C244" t="n">
-        <v>0.5724315384031902</v>
+        <v>0.5724315384031903</v>
       </c>
       <c r="D244" t="n">
         <v>0.7603152977812379</v>
@@ -4647,7 +4647,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>0.5653014780127634</v>
+        <v>0.5653014780127633</v>
       </c>
       <c r="C249" t="n">
         <v>0.5696633737708955</v>
@@ -4667,7 +4667,7 @@
         <v>0.5647494563540467</v>
       </c>
       <c r="C250" t="n">
-        <v>0.5691274717853079</v>
+        <v>0.5691274717853076</v>
       </c>
       <c r="D250" t="n">
         <v>0.7606072401712729</v>
@@ -4681,7 +4681,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="n">
-        <v>0.5642033856766312</v>
+        <v>0.5642033856766311</v>
       </c>
       <c r="C251" t="n">
         <v>0.5685973121388275</v>
@@ -4701,7 +4701,7 @@
         <v>0.5636631907514629</v>
       </c>
       <c r="C252" t="n">
-        <v>0.5680728250138295</v>
+        <v>0.5680728250138294</v>
       </c>
       <c r="D252" t="n">
         <v>0.7606072401712729</v>
@@ -4800,7 +4800,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>0.560541330808043</v>
+        <v>0.5605413308080431</v>
       </c>
       <c r="C258" t="n">
         <v>0.5650412428133353</v>
@@ -4817,7 +4817,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>0.5600402466717936</v>
+        <v>0.5600402466717938</v>
       </c>
       <c r="C259" t="n">
         <v>0.5645545923016575</v>
@@ -4834,7 +4834,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>0.5595444731281195</v>
+        <v>0.5595444731281196</v>
       </c>
       <c r="C260" t="n">
         <v>0.5640730909602344</v>
@@ -4919,7 +4919,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>0.5571429727586208</v>
+        <v>0.5571429727586207</v>
       </c>
       <c r="C265" t="n">
         <v>0.5617407017147974</v>
@@ -4936,7 +4936,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>0.5566776999113404</v>
+        <v>0.5566776999113405</v>
       </c>
       <c r="C266" t="n">
         <v>0.5612888344020741</v>
@@ -4990,7 +4990,7 @@
         <v>0.5553108253985638</v>
       </c>
       <c r="C269" t="n">
-        <v>0.559961425351965</v>
+        <v>0.5599614253519649</v>
       </c>
       <c r="D269" t="n">
         <v>0.7622615803814714</v>
@@ -5038,7 +5038,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="n">
-        <v>0.5539861206318279</v>
+        <v>0.5539861206318281</v>
       </c>
       <c r="C272" t="n">
         <v>0.5586751504641255</v>
@@ -5055,7 +5055,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>0.5535536533930369</v>
+        <v>0.5535536533930367</v>
       </c>
       <c r="C273" t="n">
         <v>0.5582552825853165</v>
@@ -5092,7 +5092,7 @@
         <v>0.5527020328738025</v>
       </c>
       <c r="C275" t="n">
-        <v>0.5574285689553004</v>
+        <v>0.5574285689553005</v>
       </c>
       <c r="D275" t="n">
         <v>0.762066952121448</v>
@@ -5126,7 +5126,7 @@
         <v>0.5518677983463437</v>
       </c>
       <c r="C277" t="n">
-        <v>0.5566188779280449</v>
+        <v>0.5566188779280448</v>
       </c>
       <c r="D277" t="n">
         <v>0.7623588945114831</v>
@@ -5140,7 +5140,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>0.5514570660808411</v>
+        <v>0.5514570660808412</v>
       </c>
       <c r="C278" t="n">
         <v>0.5562202904992709</v>
@@ -5191,7 +5191,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>0.5502497778949618</v>
+        <v>0.5502497778949619</v>
       </c>
       <c r="C281" t="n">
         <v>0.5550489722544972</v>
@@ -5208,10 +5208,10 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>0.5498554796220672</v>
+        <v>0.5498554796220673</v>
       </c>
       <c r="C282" t="n">
-        <v>0.5546665206287456</v>
+        <v>0.5546665206287457</v>
       </c>
       <c r="D282" t="n">
         <v>0.7623588945114831</v>
@@ -5242,7 +5242,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>0.5490787769760618</v>
+        <v>0.5490787769760617</v>
       </c>
       <c r="C284" t="n">
         <v>0.553913316217055</v>
@@ -5293,7 +5293,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>0.547942720646167</v>
+        <v>0.5479427206461669</v>
       </c>
       <c r="C287" t="n">
         <v>0.5528120668488583</v>
@@ -5327,7 +5327,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>0.5472041215126232</v>
+        <v>0.5472041215126233</v>
       </c>
       <c r="C289" t="n">
         <v>0.5520964137160159</v>
@@ -5347,7 +5347,7 @@
         <v>0.5468403128087015</v>
       </c>
       <c r="C290" t="n">
-        <v>0.5517440089400019</v>
+        <v>0.551744008940002</v>
       </c>
       <c r="D290" t="n">
         <v>0.7633320358115998</v>
@@ -5361,7 +5361,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>0.5464801034315331</v>
+        <v>0.546480103431533</v>
       </c>
       <c r="C291" t="n">
         <v>0.5513951610452107</v>
@@ -5378,10 +5378,10 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>0.5461234481108744</v>
+        <v>0.5461234481108745</v>
       </c>
       <c r="C292" t="n">
-        <v>0.5510498273642102</v>
+        <v>0.55104982736421</v>
       </c>
       <c r="D292" t="n">
         <v>0.7636239782016349</v>
@@ -5432,7 +5432,7 @@
         <v>0.5450743616277338</v>
       </c>
       <c r="C295" t="n">
-        <v>0.5500344915717992</v>
+        <v>0.5500344915717993</v>
       </c>
       <c r="D295" t="n">
         <v>0.7643051771117166</v>
@@ -5480,7 +5480,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0.5440556816648513</v>
+        <v>0.5440556816648514</v>
       </c>
       <c r="C298" t="n">
         <v>0.549049289714667</v>
@@ -5497,7 +5497,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>0.5437226805444916</v>
+        <v>0.5437226805444915</v>
       </c>
       <c r="C299" t="n">
         <v>0.548727397469107</v>
@@ -5514,7 +5514,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>0.5433928897351196</v>
+        <v>0.5433928897351195</v>
       </c>
       <c r="C300" t="n">
         <v>0.5484086936183129</v>
@@ -5582,7 +5582,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>0.5421050217348575</v>
+        <v>0.5421050217348576</v>
       </c>
       <c r="C304" t="n">
         <v>0.547164990640333</v>
@@ -5599,7 +5599,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="n">
-        <v>0.5417906806917224</v>
+        <v>0.5417906806917223</v>
       </c>
       <c r="C305" t="n">
         <v>0.5468616535417147</v>
@@ -5650,7 +5650,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>0.5408653433385638</v>
+        <v>0.540865343338564</v>
       </c>
       <c r="C308" t="n">
         <v>0.5459692625198563</v>
@@ -5755,7 +5755,7 @@
         <v>0.5390909280261472</v>
       </c>
       <c r="C314" t="n">
-        <v>0.5442605567655497</v>
+        <v>0.5442605567655496</v>
       </c>
       <c r="D314" t="n">
         <v>0.7647917477617751</v>
@@ -5772,7 +5772,7 @@
         <v>0.538804660409372</v>
       </c>
       <c r="C315" t="n">
-        <v>0.5439852292077335</v>
+        <v>0.5439852292077336</v>
       </c>
       <c r="D315" t="n">
         <v>0.7648890618917867</v>
@@ -5786,7 +5786,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="n">
-        <v>0.5385210057902911</v>
+        <v>0.5385210057902909</v>
       </c>
       <c r="C316" t="n">
         <v>0.5437125136504514</v>
@@ -5854,10 +5854,10 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>0.5374118507082695</v>
+        <v>0.5374118507082694</v>
       </c>
       <c r="C320" t="n">
-        <v>0.5426471183975642</v>
+        <v>0.5426471183975643</v>
       </c>
       <c r="D320" t="n">
         <v>0.7651810042818217</v>
@@ -5888,7 +5888,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>0.536872096053482</v>
+        <v>0.5368720960534822</v>
       </c>
       <c r="C322" t="n">
         <v>0.5421292537314739</v>
@@ -5905,7 +5905,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="n">
-        <v>0.5366058134867333</v>
+        <v>0.5366058134867334</v>
       </c>
       <c r="C323" t="n">
         <v>0.5418739202943688</v>
@@ -5956,7 +5956,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="n">
-        <v>0.5358209763147587</v>
+        <v>0.5358209763147586</v>
       </c>
       <c r="C326" t="n">
         <v>0.5411219511718</v>
@@ -5973,7 +5973,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="n">
-        <v>0.5355639340171562</v>
+        <v>0.5355639340171563</v>
       </c>
       <c r="C327" t="n">
         <v>0.5408758726715918</v>
@@ -6075,7 +6075,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="n">
-        <v>0.5340676383763656</v>
+        <v>0.5340676383763657</v>
       </c>
       <c r="C333" t="n">
         <v>0.539445453045634</v>
@@ -6092,7 +6092,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="n">
-        <v>0.5338256547653518</v>
+        <v>0.5338256547653517</v>
       </c>
       <c r="C334" t="n">
         <v>0.5392144649992066</v>
@@ -6112,7 +6112,7 @@
         <v>0.5335857128915602</v>
       </c>
       <c r="C335" t="n">
-        <v>0.5389855233524343</v>
+        <v>0.5389855233524344</v>
       </c>
       <c r="D335" t="n">
         <v>0.7656675749318801</v>
@@ -6126,7 +6126,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="n">
-        <v>0.5333477864774353</v>
+        <v>0.5333477864774354</v>
       </c>
       <c r="C336" t="n">
         <v>0.5387586017807778</v>
@@ -6143,7 +6143,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="n">
-        <v>0.5331118496042092</v>
+        <v>0.5331118496042094</v>
       </c>
       <c r="C337" t="n">
         <v>0.5385336742965747</v>
@@ -6180,7 +6180,7 @@
         <v>0.532645842581157</v>
       </c>
       <c r="C339" t="n">
-        <v>0.5380896993151715</v>
+        <v>0.5380896993151714</v>
       </c>
       <c r="D339" t="n">
         <v>0.7661541455819385</v>
@@ -6228,7 +6228,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>0.5319611259256846</v>
+        <v>0.5319611259256845</v>
       </c>
       <c r="C342" t="n">
         <v>0.5374380620031788</v>
@@ -6299,7 +6299,7 @@
         <v>0.5310738441272097</v>
       </c>
       <c r="C346" t="n">
-        <v>0.5365949375605508</v>
+        <v>0.5365949375605509</v>
       </c>
       <c r="D346" t="n">
         <v>0.767516543402102</v>
@@ -6398,7 +6398,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="n">
-        <v>0.5297949782324416</v>
+        <v>0.5297949782324415</v>
       </c>
       <c r="C352" t="n">
         <v>0.5353823915893843</v>
@@ -6500,7 +6500,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="n">
-        <v>0.5285745013537537</v>
+        <v>0.5285745013537539</v>
       </c>
       <c r="C358" t="n">
         <v>0.5342282894989129</v>
@@ -6517,7 +6517,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="n">
-        <v>0.5283764626097559</v>
+        <v>0.5283764626097561</v>
       </c>
       <c r="C359" t="n">
         <v>0.5340413146844825</v>
@@ -6534,7 +6534,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="n">
-        <v>0.5281799088152137</v>
+        <v>0.5281799088152138</v>
       </c>
       <c r="C360" t="n">
         <v>0.5338558245439455</v>
@@ -6585,7 +6585,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="n">
-        <v>0.5275989754038145</v>
+        <v>0.5275989754038144</v>
       </c>
       <c r="C363" t="n">
         <v>0.5333080778491293</v>
@@ -6605,7 +6605,7 @@
         <v>0.5274081810281861</v>
       </c>
       <c r="C364" t="n">
-        <v>0.5331283434406732</v>
+        <v>0.5331283434406733</v>
       </c>
       <c r="D364" t="n">
         <v>0.7665434021019852</v>
@@ -6653,7 +6653,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="n">
-        <v>0.5268441067715292</v>
+        <v>0.5268441067715294</v>
       </c>
       <c r="C367" t="n">
         <v>0.5325974387346581</v>
@@ -6673,7 +6673,7 @@
         <v>0.5266587958685065</v>
       </c>
       <c r="C368" t="n">
-        <v>0.5324231800752864</v>
+        <v>0.5324231800752866</v>
       </c>
       <c r="D368" t="n">
         <v>0.7665434021019852</v>
@@ -6687,10 +6687,10 @@
         <v>368</v>
       </c>
       <c r="B369" t="n">
-        <v>0.5264748146260027</v>
+        <v>0.5264748146260025</v>
       </c>
       <c r="C369" t="n">
-        <v>0.5322502485368656</v>
+        <v>0.5322502485368658</v>
       </c>
       <c r="D369" t="n">
         <v>0.7666407162319969</v>
@@ -6738,7 +6738,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>0.5259306901308121</v>
+        <v>0.5259306901308122</v>
       </c>
       <c r="C372" t="n">
         <v>0.531739255576789</v>
@@ -6772,7 +6772,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="n">
-        <v>0.5255743018850371</v>
+        <v>0.5255743018850372</v>
       </c>
       <c r="C374" t="n">
         <v>0.5314049381103596</v>
@@ -6823,7 +6823,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>0.5250489627053571</v>
+        <v>0.5250489627053572</v>
       </c>
       <c r="C377" t="n">
         <v>0.5309126754224712</v>
@@ -6894,7 +6894,7 @@
         <v>0.5243651643046723</v>
       </c>
       <c r="C381" t="n">
-        <v>0.5302729152160992</v>
+        <v>0.5302729152160993</v>
       </c>
       <c r="D381" t="n">
         <v>0.7659595173219151</v>
@@ -6908,7 +6908,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="n">
-        <v>0.5241970968598508</v>
+        <v>0.5241970968598509</v>
       </c>
       <c r="C382" t="n">
         <v>0.5301158446874973</v>
@@ -6928,7 +6928,7 @@
         <v>0.5240301556693797</v>
       </c>
       <c r="C383" t="n">
-        <v>0.5299598950141263</v>
+        <v>0.5299598950141264</v>
       </c>
       <c r="D383" t="n">
         <v>0.7659595173219151</v>
@@ -7013,7 +7013,7 @@
         <v>0.5232118966173582</v>
       </c>
       <c r="C388" t="n">
-        <v>0.5291965070767668</v>
+        <v>0.529196507076767</v>
       </c>
       <c r="D388" t="n">
         <v>0.7663487738419619</v>
@@ -7061,7 +7061,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="n">
-        <v>0.522733655750631</v>
+        <v>0.5227336557506309</v>
       </c>
       <c r="C391" t="n">
         <v>0.528751114608646</v>
@@ -7081,7 +7081,7 @@
         <v>0.5225762900859467</v>
       </c>
       <c r="C392" t="n">
-        <v>0.5286046852747478</v>
+        <v>0.5286046852747479</v>
       </c>
       <c r="D392" t="n">
         <v>0.7666407162319969</v>
@@ -7146,7 +7146,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>0.5219567658907167</v>
+        <v>0.5219567658907169</v>
       </c>
       <c r="C396" t="n">
         <v>0.5280288378922309</v>
@@ -7180,7 +7180,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>0.521652814375938</v>
+        <v>0.5216528143759381</v>
       </c>
       <c r="C398" t="n">
         <v>0.5277466824031605</v>
@@ -7214,7 +7214,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="n">
-        <v>0.5213526241507003</v>
+        <v>0.5213526241507004</v>
       </c>
       <c r="C400" t="n">
         <v>0.5274682591234725</v>
@@ -7248,7 +7248,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>0.5210561139057203</v>
+        <v>0.5210561139057202</v>
       </c>
       <c r="C402" t="n">
         <v>0.5271934862430091</v>
@@ -7265,7 +7265,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="n">
-        <v>0.5209092140020199</v>
+        <v>0.5209092140020201</v>
       </c>
       <c r="C403" t="n">
         <v>0.5270574437977835</v>
@@ -7316,7 +7316,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="n">
-        <v>0.5204738196205505</v>
+        <v>0.5204738196205504</v>
       </c>
       <c r="C406" t="n">
         <v>0.5266545764067758</v>
@@ -7333,7 +7333,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="n">
-        <v>0.520330425301249</v>
+        <v>0.5203304253012491</v>
       </c>
       <c r="C407" t="n">
         <v>0.5265220091864314</v>
@@ -7350,7 +7350,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="n">
-        <v>0.5201878842325645</v>
+        <v>0.5201878842325643</v>
       </c>
       <c r="C408" t="n">
         <v>0.5263902875637112</v>
@@ -7421,7 +7421,7 @@
         <v>0.5196260743809812</v>
       </c>
       <c r="C412" t="n">
-        <v>0.5258716787662543</v>
+        <v>0.5258716787662542</v>
       </c>
       <c r="D412" t="n">
         <v>0.766932658622032</v>
@@ -7435,7 +7435,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="n">
-        <v>0.5194876670842434</v>
+        <v>0.5194876670842433</v>
       </c>
       <c r="C413" t="n">
         <v>0.5257440525483669</v>
@@ -7472,7 +7472,7 @@
         <v>0.5192132475509521</v>
       </c>
       <c r="C415" t="n">
-        <v>0.5254911722234384</v>
+        <v>0.5254911722234383</v>
       </c>
       <c r="D415" t="n">
         <v>0.766932658622032</v>
@@ -7489,7 +7489,7 @@
         <v>0.5190772188814841</v>
       </c>
       <c r="C416" t="n">
-        <v>0.5253659017254634</v>
+        <v>0.5253659017254635</v>
       </c>
       <c r="D416" t="n">
         <v>0.766932658622032</v>
@@ -7537,7 +7537,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="n">
-        <v>0.5186737610071253</v>
+        <v>0.5186737610071254</v>
       </c>
       <c r="C419" t="n">
         <v>0.5249946729975827</v>
@@ -7574,7 +7574,7 @@
         <v>0.5184085678178434</v>
       </c>
       <c r="C421" t="n">
-        <v>0.5247509285066102</v>
+        <v>0.5247509285066104</v>
       </c>
       <c r="D421" t="n">
         <v>0.7673219151420786</v>
@@ -7605,7 +7605,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="n">
-        <v>0.5181463267076554</v>
+        <v>0.5181463267076555</v>
       </c>
       <c r="C423" t="n">
         <v>0.5245101066531846</v>
@@ -7639,10 +7639,10 @@
         <v>424</v>
       </c>
       <c r="B425" t="n">
-        <v>0.5178869787122118</v>
+        <v>0.5178869787122117</v>
       </c>
       <c r="C425" t="n">
-        <v>0.5242721489769558</v>
+        <v>0.524272148976956</v>
       </c>
       <c r="D425" t="n">
         <v>0.7674192292720903</v>
@@ -7741,7 +7741,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="n">
-        <v>0.5171257266043778</v>
+        <v>0.5171257266043777</v>
       </c>
       <c r="C431" t="n">
         <v>0.523574900511204</v>
@@ -7758,7 +7758,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="n">
-        <v>0.5170012282924138</v>
+        <v>0.517001228292414</v>
       </c>
       <c r="C432" t="n">
         <v>0.5234610460559764</v>
@@ -7792,7 +7792,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="n">
-        <v>0.5167542097444757</v>
+        <v>0.5167542097444756</v>
       </c>
       <c r="C434" t="n">
         <v>0.5232352961284764</v>
@@ -7826,7 +7826,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="n">
-        <v>0.5165097861468517</v>
+        <v>0.5165097861468518</v>
       </c>
       <c r="C436" t="n">
         <v>0.5230121165223085</v>
@@ -7843,10 +7843,10 @@
         <v>436</v>
       </c>
       <c r="B437" t="n">
-        <v>0.5163885318166753</v>
+        <v>0.5163885318166754</v>
       </c>
       <c r="C437" t="n">
-        <v>0.5229014752844681</v>
+        <v>0.522901475284468</v>
       </c>
       <c r="D437" t="n">
         <v>0.7674192292720903</v>
@@ -7860,7 +7860,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>0.516267907611302</v>
+        <v>0.5162679076113019</v>
       </c>
       <c r="C438" t="n">
         <v>0.5227914584250377</v>
@@ -8033,7 +8033,7 @@
         <v>0.515095026593185</v>
       </c>
       <c r="C448" t="n">
-        <v>0.5217243708566667</v>
+        <v>0.5217243708566666</v>
       </c>
       <c r="D448" t="n">
         <v>0.7677111716621253</v>
@@ -8047,7 +8047,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="n">
-        <v>0.5149809498317721</v>
+        <v>0.5149809498317722</v>
       </c>
       <c r="C449" t="n">
         <v>0.5216208495161793</v>
@@ -8064,7 +8064,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="n">
-        <v>0.5148674350937134</v>
+        <v>0.5148674350937131</v>
       </c>
       <c r="C450" t="n">
         <v>0.5215178866811037</v>
@@ -8098,7 +8098,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="n">
-        <v>0.5146420706680381</v>
+        <v>0.5146420706680382</v>
       </c>
       <c r="C452" t="n">
         <v>0.5213136164429444</v>
@@ -8149,7 +8149,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>0.5143081092921821</v>
+        <v>0.5143081092921823</v>
       </c>
       <c r="C455" t="n">
         <v>0.521011276017478</v>
@@ -8186,7 +8186,7 @@
         <v>0.514088132960835</v>
       </c>
       <c r="C457" t="n">
-        <v>0.5208123698468081</v>
+        <v>0.5208123698468082</v>
       </c>
       <c r="D457" t="n">
         <v>0.7670299727520435</v>
@@ -8234,7 +8234,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="n">
-        <v>0.5137620668854197</v>
+        <v>0.5137620668854198</v>
       </c>
       <c r="C460" t="n">
         <v>0.5205178990133825</v>
@@ -8251,7 +8251,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="n">
-        <v>0.5136543985192918</v>
+        <v>0.513654398519292</v>
       </c>
       <c r="C461" t="n">
         <v>0.5204207609508389</v>
@@ -8268,7 +8268,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="n">
-        <v>0.5135472324295934</v>
+        <v>0.5135472324295933</v>
       </c>
       <c r="C462" t="n">
         <v>0.5203241249794511</v>
@@ -8305,7 +8305,7 @@
         <v>0.513334388465421</v>
       </c>
       <c r="C464" t="n">
-        <v>0.5201323420513946</v>
+        <v>0.5201323420513947</v>
       </c>
       <c r="D464" t="n">
         <v>0.7670299727520435</v>
@@ -8421,7 +8421,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="n">
-        <v>0.5126045843798017</v>
+        <v>0.5126045843798018</v>
       </c>
       <c r="C471" t="n">
         <v>0.5194762984980825</v>
@@ -8472,7 +8472,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="n">
-        <v>0.5122987608236391</v>
+        <v>0.512298760823639</v>
       </c>
       <c r="C474" t="n">
         <v>0.5192021330266799</v>
@@ -8489,7 +8489,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="n">
-        <v>0.5121977148034877</v>
+        <v>0.5121977148034879</v>
       </c>
       <c r="C475" t="n">
         <v>0.5191116491042075</v>
@@ -8591,7 +8591,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="n">
-        <v>0.5116005478178235</v>
+        <v>0.5116005478178234</v>
       </c>
       <c r="C481" t="n">
         <v>0.5185779876611274</v>
@@ -8608,7 +8608,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="n">
-        <v>0.5115025002983972</v>
+        <v>0.5115025002983973</v>
       </c>
       <c r="C482" t="n">
         <v>0.5184905514476986</v>
@@ -8625,10 +8625,10 @@
         <v>482</v>
       </c>
       <c r="B483" t="n">
-        <v>0.5114048650801167</v>
+        <v>0.5114048650801166</v>
       </c>
       <c r="C483" t="n">
-        <v>0.5184035367397044</v>
+        <v>0.5184035367397045</v>
       </c>
       <c r="D483" t="n">
         <v>0.7656675749318801</v>
@@ -8696,7 +8696,7 @@
         <v>0.5110183690460347</v>
       </c>
       <c r="C487" t="n">
-        <v>0.5180596266814799</v>
+        <v>0.51805962668148</v>
       </c>
       <c r="D487" t="n">
         <v>0.7659595173219151</v>
@@ -8710,10 +8710,10 @@
         <v>487</v>
       </c>
       <c r="B488" t="n">
-        <v>0.5109227369320386</v>
+        <v>0.5109227369320385</v>
       </c>
       <c r="C488" t="n">
-        <v>0.5179746701424455</v>
+        <v>0.5179746701424456</v>
       </c>
       <c r="D488" t="n">
         <v>0.7659595173219151</v>
@@ -8761,7 +8761,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="n">
-        <v>0.5106381602203867</v>
+        <v>0.5106381602203865</v>
       </c>
       <c r="C491" t="n">
         <v>0.5177222003874822</v>
@@ -8812,7 +8812,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="n">
-        <v>0.5103569843483324</v>
+        <v>0.5103569843483323</v>
       </c>
       <c r="C494" t="n">
         <v>0.5174732663899869</v>
@@ -8863,7 +8863,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="n">
-        <v>0.5100791097148464</v>
+        <v>0.5100791097148463</v>
       </c>
       <c r="C497" t="n">
         <v>0.5172277883366223</v>
@@ -8917,7 +8917,7 @@
         <v>0.5098044383567074</v>
       </c>
       <c r="C500" t="n">
-        <v>0.5169856893566153</v>
+        <v>0.5169856893566154</v>
       </c>
       <c r="D500" t="n">
         <v>0.7666407162319969</v>
@@ -8948,10 +8948,10 @@
         <v>501</v>
       </c>
       <c r="B502" t="n">
-        <v>0.5096230560238719</v>
+        <v>0.509623056023872</v>
       </c>
       <c r="C502" t="n">
-        <v>0.5168261306329073</v>
+        <v>0.5168261306329072</v>
       </c>
       <c r="D502" t="n">
         <v>0.7666407162319969</v>
@@ -8965,10 +8965,10 @@
         <v>502</v>
       </c>
       <c r="B503" t="n">
-        <v>0.5095328738162607</v>
+        <v>0.5095328738162606</v>
       </c>
       <c r="C503" t="n">
-        <v>0.5167468954322846</v>
+        <v>0.5167468954322847</v>
       </c>
       <c r="D503" t="n">
         <v>0.7666407162319969</v>
@@ -8982,7 +8982,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="n">
-        <v>0.509443026235899</v>
+        <v>0.5094430262358989</v>
       </c>
       <c r="C504" t="n">
         <v>0.516668019521025</v>
@@ -9016,7 +9016,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="n">
-        <v>0.509264321014008</v>
+        <v>0.5092643210140079</v>
       </c>
       <c r="C506" t="n">
         <v>0.5165113353103662</v>
@@ -9036,7 +9036,7 @@
         <v>0.5091754564380271</v>
       </c>
       <c r="C507" t="n">
-        <v>0.5164335219640915</v>
+        <v>0.5164335219640914</v>
       </c>
       <c r="D507" t="n">
         <v>0.7666407162319969</v>
@@ -9050,7 +9050,7 @@
         <v>507</v>
       </c>
       <c r="B508" t="n">
-        <v>0.5090869126194272</v>
+        <v>0.5090869126194271</v>
       </c>
       <c r="C508" t="n">
         <v>0.516356057812657</v>
@@ -9118,7 +9118,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="n">
-        <v>0.5087358764649056</v>
+        <v>0.5087358764649057</v>
       </c>
       <c r="C512" t="n">
         <v>0.5160496447399076</v>
@@ -9169,7 +9169,7 @@
         <v>514</v>
       </c>
       <c r="B515" t="n">
-        <v>0.5084758003688261</v>
+        <v>0.508475800368826</v>
       </c>
       <c r="C515" t="n">
         <v>0.5158233847778232</v>
@@ -9271,7 +9271,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="n">
-        <v>0.5079634867101329</v>
+        <v>0.5079634867101328</v>
       </c>
       <c r="C521" t="n">
         <v>0.5153797296670177</v>
@@ -9308,7 +9308,7 @@
         <v>0.5077949406532911</v>
       </c>
       <c r="C523" t="n">
-        <v>0.5152344082257728</v>
+        <v>0.5152344082257729</v>
       </c>
       <c r="D523" t="n">
         <v>0.767516543402102</v>
@@ -9322,7 +9322,7 @@
         <v>523</v>
       </c>
       <c r="B524" t="n">
-        <v>0.50771107002307</v>
+        <v>0.5077110700230699</v>
       </c>
       <c r="C524" t="n">
         <v>0.5151622188567014</v>
@@ -9339,7 +9339,7 @@
         <v>524</v>
       </c>
       <c r="B525" t="n">
-        <v>0.5076274632934755</v>
+        <v>0.5076274632934756</v>
       </c>
       <c r="C525" t="n">
         <v>0.5150903410391495</v>
@@ -9424,7 +9424,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="n">
-        <v>0.5072132741409309</v>
+        <v>0.507213274140931</v>
       </c>
       <c r="C530" t="n">
         <v>0.514735556498367</v>
@@ -9441,7 +9441,7 @@
         <v>530</v>
       </c>
       <c r="B531" t="n">
-        <v>0.5071311825023215</v>
+        <v>0.5071311825023214</v>
       </c>
       <c r="C531" t="n">
         <v>0.514665507032641</v>
@@ -9461,7 +9461,7 @@
         <v>0.5070493320563537</v>
       </c>
       <c r="C532" t="n">
-        <v>0.5145957556436681</v>
+        <v>0.514595755643668</v>
       </c>
       <c r="D532" t="n">
         <v>0.7683923705722071</v>
@@ -9492,7 +9492,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="n">
-        <v>0.5068863418796465</v>
+        <v>0.5068863418796464</v>
       </c>
       <c r="C534" t="n">
         <v>0.5144571396917363</v>
@@ -9509,7 +9509,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="n">
-        <v>0.5068051957344423</v>
+        <v>0.5068051957344424</v>
       </c>
       <c r="C535" t="n">
         <v>0.5143882714615833</v>
@@ -9662,7 +9662,7 @@
         <v>543</v>
       </c>
       <c r="B544" t="n">
-        <v>0.5060847757845625</v>
+        <v>0.5060847757845622</v>
       </c>
       <c r="C544" t="n">
         <v>0.5137813258133429</v>
@@ -9696,7 +9696,7 @@
         <v>545</v>
       </c>
       <c r="B546" t="n">
-        <v>0.5059269626301871</v>
+        <v>0.505926962630187</v>
       </c>
       <c r="C546" t="n">
         <v>0.5136495163804425</v>
@@ -9713,7 +9713,7 @@
         <v>546</v>
       </c>
       <c r="B547" t="n">
-        <v>0.5058483482823023</v>
+        <v>0.5058483482823024</v>
       </c>
       <c r="C547" t="n">
         <v>0.513584019303261</v>
@@ -9747,7 +9747,7 @@
         <v>548</v>
       </c>
       <c r="B549" t="n">
-        <v>0.5056916886982126</v>
+        <v>0.5056916886982127</v>
       </c>
       <c r="C549" t="n">
         <v>0.5134538314974475</v>
@@ -9764,7 +9764,7 @@
         <v>549</v>
       </c>
       <c r="B550" t="n">
-        <v>0.5056136373753473</v>
+        <v>0.5056136373753474</v>
       </c>
       <c r="C550" t="n">
         <v>0.5133891371693483</v>
@@ -9798,7 +9798,7 @@
         <v>551</v>
       </c>
       <c r="B552" t="n">
-        <v>0.5054580766008369</v>
+        <v>0.5054580766008367</v>
       </c>
       <c r="C552" t="n">
         <v>0.5132605385720341</v>
@@ -9866,7 +9866,7 @@
         <v>555</v>
       </c>
       <c r="B556" t="n">
-        <v>0.505149039654548</v>
+        <v>0.5051490396545479</v>
       </c>
       <c r="C556" t="n">
         <v>0.5130064496804732</v>
@@ -9903,7 +9903,7 @@
         <v>0.5049955171487643</v>
       </c>
       <c r="C558" t="n">
-        <v>0.5128809289664387</v>
+        <v>0.5128809289664388</v>
       </c>
       <c r="D558" t="n">
         <v>0.7685869988322305</v>
@@ -9951,7 +9951,7 @@
         <v>560</v>
       </c>
       <c r="B561" t="n">
-        <v>0.5047664153384672</v>
+        <v>0.5047664153384673</v>
       </c>
       <c r="C561" t="n">
         <v>0.512694508211299</v>
@@ -9985,7 +9985,7 @@
         <v>562</v>
       </c>
       <c r="B563" t="n">
-        <v>0.5046144374504927</v>
+        <v>0.5046144374504928</v>
       </c>
       <c r="C563" t="n">
         <v>0.5125714439529014</v>
@@ -10002,7 +10002,7 @@
         <v>563</v>
       </c>
       <c r="B564" t="n">
-        <v>0.5045386677523218</v>
+        <v>0.5045386677523217</v>
       </c>
       <c r="C564" t="n">
         <v>0.5125102703289904</v>
@@ -10036,10 +10036,10 @@
         <v>565</v>
       </c>
       <c r="B566" t="n">
-        <v>0.5043875545089848</v>
+        <v>0.5043875545089849</v>
       </c>
       <c r="C566" t="n">
-        <v>0.5123886291069856</v>
+        <v>0.5123886291069857</v>
       </c>
       <c r="D566" t="n">
         <v>0.7685869988322305</v>
@@ -10053,10 +10053,10 @@
         <v>566</v>
       </c>
       <c r="B567" t="n">
-        <v>0.5043122062232248</v>
+        <v>0.5043122062232249</v>
       </c>
       <c r="C567" t="n">
-        <v>0.5123281569975651</v>
+        <v>0.5123281569975652</v>
       </c>
       <c r="D567" t="n">
         <v>0.7685869988322305</v>
@@ -10070,7 +10070,7 @@
         <v>567</v>
       </c>
       <c r="B568" t="n">
-        <v>0.5042369937857561</v>
+        <v>0.5042369937857563</v>
       </c>
       <c r="C568" t="n">
         <v>0.5122679141478497</v>
@@ -10087,7 +10087,7 @@
         <v>568</v>
       </c>
       <c r="B569" t="n">
-        <v>0.5041619150099595</v>
+        <v>0.5041619150099597</v>
       </c>
       <c r="C569" t="n">
         <v>0.5122078982007057</v>
@@ -10138,7 +10138,7 @@
         <v>571</v>
       </c>
       <c r="B572" t="n">
-        <v>0.5039374600361319</v>
+        <v>0.5039374600361318</v>
       </c>
       <c r="C572" t="n">
         <v>0.512029187586825</v>
@@ -10155,7 +10155,7 @@
         <v>572</v>
       </c>
       <c r="B573" t="n">
-        <v>0.5038628957394611</v>
+        <v>0.503862895739461</v>
       </c>
       <c r="C573" t="n">
         <v>0.5119700548586925</v>
@@ -10206,7 +10206,7 @@
         <v>575</v>
       </c>
       <c r="B576" t="n">
-        <v>0.5036399407051171</v>
+        <v>0.5036399407051172</v>
       </c>
       <c r="C576" t="n">
         <v>0.5117939332896961</v>
@@ -10226,7 +10226,7 @@
         <v>0.5035658632542472</v>
       </c>
       <c r="C577" t="n">
-        <v>0.5117356428672366</v>
+        <v>0.5117356428672367</v>
       </c>
       <c r="D577" t="n">
         <v>0.7691708836123005</v>
@@ -10240,7 +10240,7 @@
         <v>577</v>
       </c>
       <c r="B578" t="n">
-        <v>0.5034919040084493</v>
+        <v>0.5034919040084492</v>
       </c>
       <c r="C578" t="n">
         <v>0.5116775563604011</v>
@@ -10393,7 +10393,7 @@
         <v>586</v>
       </c>
       <c r="B587" t="n">
-        <v>0.5028314416136322</v>
+        <v>0.5028314416136321</v>
       </c>
       <c r="C587" t="n">
         <v>0.5111634982450259</v>
@@ -10410,7 +10410,7 @@
         <v>587</v>
       </c>
       <c r="B588" t="n">
-        <v>0.5027586225338194</v>
+        <v>0.5027586225338195</v>
       </c>
       <c r="C588" t="n">
         <v>0.5111072984034497</v>
@@ -10444,7 +10444,7 @@
         <v>589</v>
       </c>
       <c r="B590" t="n">
-        <v>0.5026133235840132</v>
+        <v>0.5026133235840131</v>
       </c>
       <c r="C590" t="n">
         <v>0.5109954160112199</v>
@@ -10478,7 +10478,7 @@
         <v>591</v>
       </c>
       <c r="B592" t="n">
-        <v>0.5024684803044894</v>
+        <v>0.5024684803044895</v>
       </c>
       <c r="C592" t="n">
         <v>0.5108842053485154</v>
@@ -10529,10 +10529,10 @@
         <v>594</v>
       </c>
       <c r="B595" t="n">
-        <v>0.5022520838698986</v>
+        <v>0.5022520838698985</v>
       </c>
       <c r="C595" t="n">
-        <v>0.5107186032192329</v>
+        <v>0.5107186032192328</v>
       </c>
       <c r="D595" t="n">
         <v>0.7691708836123005</v>
@@ -10648,7 +10648,7 @@
         <v>601</v>
       </c>
       <c r="B602" t="n">
-        <v>0.5017513935075111</v>
+        <v>0.5017513935075112</v>
       </c>
       <c r="C602" t="n">
         <v>0.510337530317052</v>
@@ -10665,7 +10665,7 @@
         <v>602</v>
       </c>
       <c r="B603" t="n">
-        <v>0.5016803753785211</v>
+        <v>0.5016803753785212</v>
       </c>
       <c r="C603" t="n">
         <v>0.5102836699089863</v>
@@ -10682,7 +10682,7 @@
         <v>603</v>
       </c>
       <c r="B604" t="n">
-        <v>0.5016094906416568</v>
+        <v>0.5016094906416567</v>
       </c>
       <c r="C604" t="n">
         <v>0.5102299487435148</v>
@@ -10733,7 +10733,7 @@
         <v>606</v>
       </c>
       <c r="B607" t="n">
-        <v>0.5013976598005094</v>
+        <v>0.5013976598005095</v>
       </c>
       <c r="C607" t="n">
         <v>0.510069606040819</v>
@@ -10801,7 +10801,7 @@
         <v>610</v>
       </c>
       <c r="B611" t="n">
-        <v>0.501117230567967</v>
+        <v>0.5011172305679669</v>
       </c>
       <c r="C611" t="n">
         <v>0.50985768608176</v>
@@ -10835,7 +10835,7 @@
         <v>612</v>
       </c>
       <c r="B613" t="n">
-        <v>0.5009779234494615</v>
+        <v>0.5009779234494616</v>
       </c>
       <c r="C613" t="n">
         <v>0.5097525112822338</v>
@@ -10872,7 +10872,7 @@
         <v>0.5008392484007946</v>
       </c>
       <c r="C615" t="n">
-        <v>0.5096478535203022</v>
+        <v>0.5096478535203023</v>
       </c>
       <c r="D615" t="n">
         <v>0.7693655118723238</v>
@@ -10954,7 +10954,7 @@
         <v>619</v>
       </c>
       <c r="B620" t="n">
-        <v>0.5004954550184708</v>
+        <v>0.5004954550184709</v>
       </c>
       <c r="C620" t="n">
         <v>0.5093884566614308</v>
@@ -11008,7 +11008,7 @@
         <v>0.5002912550136224</v>
       </c>
       <c r="C623" t="n">
-        <v>0.5092343585710761</v>
+        <v>0.509234358571076</v>
       </c>
       <c r="D623" t="n">
         <v>0.7691708836123005</v>
@@ -11073,7 +11073,7 @@
         <v>626</v>
       </c>
       <c r="B627" t="n">
-        <v>0.5000215217978179</v>
+        <v>0.500021521797818</v>
       </c>
       <c r="C627" t="n">
         <v>0.5090307014756987</v>
@@ -11093,7 +11093,7 @@
         <v>0.4999545518758995</v>
       </c>
       <c r="C628" t="n">
-        <v>0.5089801119667694</v>
+        <v>0.5089801119667693</v>
       </c>
       <c r="D628" t="n">
         <v>0.7697547683923706</v>
@@ -11107,10 +11107,10 @@
         <v>628</v>
       </c>
       <c r="B629" t="n">
-        <v>0.4998877700575312</v>
+        <v>0.499887770057531</v>
       </c>
       <c r="C629" t="n">
-        <v>0.5089296530749177</v>
+        <v>0.5089296530749176</v>
       </c>
       <c r="D629" t="n">
         <v>0.7694628260023355</v>
@@ -11127,7 +11127,7 @@
         <v>0.4998211774938273</v>
       </c>
       <c r="C630" t="n">
-        <v>0.508879325165572</v>
+        <v>0.5088793251655719</v>
       </c>
       <c r="D630" t="n">
         <v>0.7694628260023355</v>
@@ -11161,7 +11161,7 @@
         <v>0.4996885640725817</v>
       </c>
       <c r="C632" t="n">
-        <v>0.5087790637281308</v>
+        <v>0.5087790637281306</v>
       </c>
       <c r="D632" t="n">
         <v>0.7695601401323472</v>
@@ -11209,7 +11209,7 @@
         <v>634</v>
       </c>
       <c r="B635" t="n">
-        <v>0.4994910844666116</v>
+        <v>0.4994910844666114</v>
       </c>
       <c r="C635" t="n">
         <v>0.5086296625225231</v>
@@ -11260,7 +11260,7 @@
         <v>637</v>
       </c>
       <c r="B638" t="n">
-        <v>0.4992953442660861</v>
+        <v>0.4992953442660862</v>
       </c>
       <c r="C638" t="n">
         <v>0.5084814571581352</v>
@@ -11311,7 +11311,7 @@
         <v>640</v>
       </c>
       <c r="B641" t="n">
-        <v>0.4991013458557722</v>
+        <v>0.4991013458557723</v>
       </c>
       <c r="C641" t="n">
         <v>0.508334452709591</v>
@@ -11430,7 +11430,7 @@
         <v>647</v>
       </c>
       <c r="B648" t="n">
-        <v>0.4986553962608886</v>
+        <v>0.4986553962608887</v>
       </c>
       <c r="C648" t="n">
         <v>0.5079961155678815</v>
@@ -11552,7 +11552,7 @@
         <v>0.498218592120678</v>
       </c>
       <c r="C655" t="n">
-        <v>0.5076642626401887</v>
+        <v>0.5076642626401886</v>
       </c>
       <c r="D655" t="n">
         <v>0.7695601401323472</v>
@@ -11654,7 +11654,7 @@
         <v>0.4978511135840619</v>
       </c>
       <c r="C661" t="n">
-        <v>0.5073848589744541</v>
+        <v>0.507384858974454</v>
       </c>
       <c r="D661" t="n">
         <v>0.7695601401323472</v>
@@ -11671,7 +11671,7 @@
         <v>0.497790461689248</v>
       </c>
       <c r="C662" t="n">
-        <v>0.5073387335236483</v>
+        <v>0.5073387335236482</v>
       </c>
       <c r="D662" t="n">
         <v>0.7697547683923706</v>
@@ -11719,7 +11719,7 @@
         <v>664</v>
       </c>
       <c r="B665" t="n">
-        <v>0.4976094893645584</v>
+        <v>0.4976094893645583</v>
       </c>
       <c r="C665" t="n">
         <v>0.5072010991688376</v>
@@ -11770,7 +11770,7 @@
         <v>667</v>
       </c>
       <c r="B668" t="n">
-        <v>0.4974299532317386</v>
+        <v>0.4974299532317387</v>
       </c>
       <c r="C668" t="n">
         <v>0.50706456019154</v>
@@ -11824,7 +11824,7 @@
         <v>0.4972518028201228</v>
       </c>
       <c r="C671" t="n">
-        <v>0.5069290928909382</v>
+        <v>0.5069290928909383</v>
       </c>
       <c r="D671" t="n">
         <v>0.7701440249124173</v>
@@ -11838,7 +11838,7 @@
         <v>671</v>
       </c>
       <c r="B672" t="n">
-        <v>0.4971927185427547</v>
+        <v>0.4971927185427548</v>
       </c>
       <c r="C672" t="n">
         <v>0.5068841710359029</v>
@@ -11872,7 +11872,7 @@
         <v>673</v>
       </c>
       <c r="B674" t="n">
-        <v>0.4970749875845155</v>
+        <v>0.4970749875845154</v>
       </c>
       <c r="C674" t="n">
         <v>0.5067946726240752</v>
@@ -11923,7 +11923,7 @@
         <v>676</v>
       </c>
       <c r="B677" t="n">
-        <v>0.4968994574359074</v>
+        <v>0.4968994574359075</v>
       </c>
       <c r="C677" t="n">
         <v>0.5066612741253047</v>
@@ -11974,7 +11974,7 @@
         <v>679</v>
       </c>
       <c r="B680" t="n">
-        <v>0.4967251631598639</v>
+        <v>0.4967251631598638</v>
       </c>
       <c r="C680" t="n">
         <v>0.5065288717747468</v>
@@ -12025,7 +12025,7 @@
         <v>682</v>
       </c>
       <c r="B683" t="n">
-        <v>0.4965520567350394</v>
+        <v>0.4965520567350395</v>
       </c>
       <c r="C683" t="n">
         <v>0.5063974398176964</v>
@@ -12076,7 +12076,7 @@
         <v>685</v>
       </c>
       <c r="B686" t="n">
-        <v>0.4963800915652778</v>
+        <v>0.4963800915652777</v>
       </c>
       <c r="C686" t="n">
         <v>0.50626695253911</v>
@@ -12178,7 +12178,7 @@
         <v>691</v>
       </c>
       <c r="B692" t="n">
-        <v>0.4960394066267002</v>
+        <v>0.4960394066267004</v>
       </c>
       <c r="C692" t="n">
         <v>0.5060087101308836</v>
@@ -12232,7 +12232,7 @@
         <v>0.4958706019338535</v>
       </c>
       <c r="C695" t="n">
-        <v>0.505880904819909</v>
+        <v>0.5058809048199091</v>
       </c>
       <c r="D695" t="n">
         <v>0.7708252238224991</v>
@@ -12283,7 +12283,7 @@
         <v>0.4957027687099386</v>
       </c>
       <c r="C698" t="n">
-        <v>0.5057539439479045</v>
+        <v>0.5057539439479044</v>
       </c>
       <c r="D698" t="n">
         <v>0.7716037368625924</v>
@@ -12314,7 +12314,7 @@
         <v>699</v>
       </c>
       <c r="B700" t="n">
-        <v>0.4955914007027781</v>
+        <v>0.4955914007027782</v>
       </c>
       <c r="C700" t="n">
         <v>0.5056697605863544</v>
@@ -12399,7 +12399,7 @@
         <v>704</v>
       </c>
       <c r="B705" t="n">
-        <v>0.4953147247931589</v>
+        <v>0.4953147247931587</v>
       </c>
       <c r="C705" t="n">
         <v>0.5054608513848448</v>
@@ -12433,7 +12433,7 @@
         <v>706</v>
       </c>
       <c r="B707" t="n">
-        <v>0.4952047250009724</v>
+        <v>0.4952047250009723</v>
       </c>
       <c r="C707" t="n">
         <v>0.5053778893574866</v>
@@ -12450,7 +12450,7 @@
         <v>707</v>
       </c>
       <c r="B708" t="n">
-        <v>0.4951498638365468</v>
+        <v>0.4951498638365469</v>
       </c>
       <c r="C708" t="n">
         <v>0.5053365338924337</v>
@@ -12501,7 +12501,7 @@
         <v>710</v>
       </c>
       <c r="B711" t="n">
-        <v>0.4949858209983333</v>
+        <v>0.4949858209983334</v>
       </c>
       <c r="C711" t="n">
         <v>0.5052129597470042</v>
@@ -12606,7 +12606,7 @@
         <v>0.4946600659719546</v>
       </c>
       <c r="C717" t="n">
-        <v>0.5049679534967685</v>
+        <v>0.5049679534967686</v>
       </c>
       <c r="D717" t="n">
         <v>0.7723822499026859</v>
@@ -12671,7 +12671,7 @@
         <v>720</v>
       </c>
       <c r="B721" t="n">
-        <v>0.4944445288586331</v>
+        <v>0.494444528858633</v>
       </c>
       <c r="C721" t="n">
         <v>0.5048061339738823</v>
@@ -12705,7 +12705,7 @@
         <v>722</v>
       </c>
       <c r="B723" t="n">
-        <v>0.4943372256710896</v>
+        <v>0.4943372256710897</v>
       </c>
       <c r="C723" t="n">
         <v>0.5047256610574857</v>
@@ -12824,7 +12824,7 @@
         <v>729</v>
       </c>
       <c r="B730" t="n">
-        <v>0.4939639774615208</v>
+        <v>0.4939639774615207</v>
       </c>
       <c r="C730" t="n">
         <v>0.5044461971766891</v>
@@ -12875,7 +12875,7 @@
         <v>732</v>
       </c>
       <c r="B733" t="n">
-        <v>0.4938050611533281</v>
+        <v>0.493805061153328</v>
       </c>
       <c r="C733" t="n">
         <v>0.5043274267731075</v>
@@ -12895,7 +12895,7 @@
         <v>0.4937522223355655</v>
       </c>
       <c r="C734" t="n">
-        <v>0.5042879647337202</v>
+        <v>0.5042879647337201</v>
       </c>
       <c r="D734" t="n">
         <v>0.7723822499026859</v>
@@ -12980,7 +12980,7 @@
         <v>0.4934889909090661</v>
       </c>
       <c r="C739" t="n">
-        <v>0.5040915841471791</v>
+        <v>0.504091584147179</v>
       </c>
       <c r="D739" t="n">
         <v>0.7724795640326976</v>
@@ -13014,7 +13014,7 @@
         <v>0.4933841327536284</v>
       </c>
       <c r="C741" t="n">
-        <v>0.5040134530854152</v>
+        <v>0.5040134530854151</v>
       </c>
       <c r="D741" t="n">
         <v>0.7723822499026859</v>
@@ -13028,10 +13028,10 @@
         <v>741</v>
       </c>
       <c r="B742" t="n">
-        <v>0.4933317936722203</v>
+        <v>0.4933317936722204</v>
       </c>
       <c r="C742" t="n">
-        <v>0.5039744751412237</v>
+        <v>0.5039744751412238</v>
       </c>
       <c r="D742" t="n">
         <v>0.7727715064227326</v>
@@ -13082,7 +13082,7 @@
         <v>0.4931751274287283</v>
       </c>
       <c r="C745" t="n">
-        <v>0.5038578838274025</v>
+        <v>0.5038578838274024</v>
       </c>
       <c r="D745" t="n">
         <v>0.7727715064227326</v>
@@ -13113,10 +13113,10 @@
         <v>746</v>
       </c>
       <c r="B747" t="n">
-        <v>0.4930709684473946</v>
+        <v>0.4930709684473947</v>
       </c>
       <c r="C747" t="n">
-        <v>0.5037804352949373</v>
+        <v>0.5037804352949372</v>
       </c>
       <c r="D747" t="n">
         <v>0.7726741922927209</v>
@@ -13150,7 +13150,7 @@
         <v>0.4929670309285897</v>
       </c>
       <c r="C749" t="n">
-        <v>0.5037032040714093</v>
+        <v>0.5037032040714092</v>
       </c>
       <c r="D749" t="n">
         <v>0.7726741922927209</v>
@@ -13266,7 +13266,7 @@
         <v>755</v>
       </c>
       <c r="B756" t="n">
-        <v>0.4926049139646846</v>
+        <v>0.4926049139646845</v>
       </c>
       <c r="C756" t="n">
         <v>0.5034345351726156</v>
@@ -13283,7 +13283,7 @@
         <v>756</v>
       </c>
       <c r="B757" t="n">
-        <v>0.4925533854002017</v>
+        <v>0.4925533854002018</v>
       </c>
       <c r="C757" t="n">
         <v>0.5033963542244576</v>
@@ -13303,7 +13303,7 @@
         <v>0.4925019054920241</v>
       </c>
       <c r="C758" t="n">
-        <v>0.5033582216050148</v>
+        <v>0.5033582216050149</v>
       </c>
       <c r="D758" t="n">
         <v>0.772966134682756</v>
@@ -13405,7 +13405,7 @@
         <v>0.4921940127037932</v>
       </c>
       <c r="C764" t="n">
-        <v>0.5031304092054874</v>
+        <v>0.5031304092054872</v>
       </c>
       <c r="D764" t="n">
         <v>0.7733553912028026</v>
@@ -13453,7 +13453,7 @@
         <v>766</v>
       </c>
       <c r="B767" t="n">
-        <v>0.4920406730854834</v>
+        <v>0.4920406730854835</v>
       </c>
       <c r="C767" t="n">
         <v>0.5030171104260329</v>
@@ -13487,7 +13487,7 @@
         <v>768</v>
       </c>
       <c r="B769" t="n">
-        <v>0.491938660502979</v>
+        <v>0.4919386605029791</v>
       </c>
       <c r="C769" t="n">
         <v>0.5029417931095028</v>
@@ -13555,7 +13555,7 @@
         <v>772</v>
       </c>
       <c r="B773" t="n">
-        <v>0.4917351278297167</v>
+        <v>0.4917351278297166</v>
       </c>
       <c r="C773" t="n">
         <v>0.5027916565303625</v>
@@ -13643,7 +13643,7 @@
         <v>0.4914815894012931</v>
       </c>
       <c r="C778" t="n">
-        <v>0.5026048790287605</v>
+        <v>0.5026048790287604</v>
       </c>
       <c r="D778" t="n">
         <v>0.773841961852861</v>
@@ -13674,7 +13674,7 @@
         <v>779</v>
       </c>
       <c r="B780" t="n">
-        <v>0.4913804330847876</v>
+        <v>0.4913804330847877</v>
       </c>
       <c r="C780" t="n">
         <v>0.5025304337492787</v>
@@ -13725,7 +13725,7 @@
         <v>782</v>
       </c>
       <c r="B783" t="n">
-        <v>0.4912289630127696</v>
+        <v>0.4912289630127697</v>
       </c>
       <c r="C783" t="n">
         <v>0.5024190391723754</v>
@@ -13827,10 +13827,10 @@
         <v>788</v>
       </c>
       <c r="B789" t="n">
-        <v>0.4909269243685505</v>
+        <v>0.4909269243685506</v>
       </c>
       <c r="C789" t="n">
-        <v>0.502197191315419</v>
+        <v>0.5021971913154188</v>
       </c>
       <c r="D789" t="n">
         <v>0.7744258466329311</v>
@@ -13861,7 +13861,7 @@
         <v>790</v>
       </c>
       <c r="B791" t="n">
-        <v>0.4908264974231237</v>
+        <v>0.4908264974231238</v>
       </c>
       <c r="C791" t="n">
         <v>0.5021235088097687</v>
@@ -13881,7 +13881,7 @@
         <v>0.4907763291448767</v>
       </c>
       <c r="C792" t="n">
-        <v>0.5020867157945319</v>
+        <v>0.502086715794532</v>
       </c>
       <c r="D792" t="n">
         <v>0.7744258466329311</v>
@@ -13912,10 +13912,10 @@
         <v>793</v>
       </c>
       <c r="B794" t="n">
-        <v>0.4906760806254082</v>
+        <v>0.4906760806254081</v>
       </c>
       <c r="C794" t="n">
-        <v>0.5020132243343473</v>
+        <v>0.5020132243343474</v>
       </c>
       <c r="D794" t="n">
         <v>0.7744258466329311</v>
@@ -13949,7 +13949,7 @@
         <v>0.4905759464012298</v>
       </c>
       <c r="C796" t="n">
-        <v>0.5019398564927523</v>
+        <v>0.5019398564927524</v>
       </c>
       <c r="D796" t="n">
         <v>0.7745231607629428</v>
@@ -14014,7 +14014,7 @@
         <v>799</v>
       </c>
       <c r="B800" t="n">
-        <v>0.4903760063170015</v>
+        <v>0.4903760063170014</v>
       </c>
       <c r="C800" t="n">
         <v>0.5017934801802149</v>
@@ -14184,7 +14184,7 @@
         <v>809</v>
       </c>
       <c r="B810" t="n">
-        <v>0.4898779090687807</v>
+        <v>0.4898779090687808</v>
       </c>
       <c r="C810" t="n">
         <v>0.5014295107588334</v>
@@ -14204,7 +14204,7 @@
         <v>0.4898282255886139</v>
       </c>
       <c r="C811" t="n">
-        <v>0.5013932601144678</v>
+        <v>0.5013932601144677</v>
       </c>
       <c r="D811" t="n">
         <v>0.7745231607629428</v>
@@ -14252,10 +14252,10 @@
         <v>813</v>
       </c>
       <c r="B814" t="n">
-        <v>0.4896793016920931</v>
+        <v>0.4896793016920932</v>
       </c>
       <c r="C814" t="n">
-        <v>0.5012846596625607</v>
+        <v>0.5012846596625606</v>
       </c>
       <c r="D814" t="n">
         <v>0.7744258466329311</v>
@@ -14269,7 +14269,7 @@
         <v>814</v>
       </c>
       <c r="B815" t="n">
-        <v>0.4896297012955425</v>
+        <v>0.4896297012955424</v>
       </c>
       <c r="C815" t="n">
         <v>0.5012485090998298</v>
@@ -14306,7 +14306,7 @@
         <v>0.4895305595969923</v>
       </c>
       <c r="C817" t="n">
-        <v>0.5011762807743166</v>
+        <v>0.5011762807743165</v>
       </c>
       <c r="D817" t="n">
         <v>0.7744258466329311</v>
@@ -14320,7 +14320,7 @@
         <v>817</v>
       </c>
       <c r="B818" t="n">
-        <v>0.4894810175564885</v>
+        <v>0.4894810175564886</v>
       </c>
       <c r="C818" t="n">
         <v>0.5011402025000509</v>
@@ -14388,7 +14388,7 @@
         <v>821</v>
       </c>
       <c r="B822" t="n">
-        <v>0.4892830330295339</v>
+        <v>0.489283033029534</v>
       </c>
       <c r="C822" t="n">
         <v>0.5009961228960119</v>
@@ -14493,7 +14493,7 @@
         <v>0.4889865689023728</v>
       </c>
       <c r="C828" t="n">
-        <v>0.5007806782834829</v>
+        <v>0.500780678283483</v>
       </c>
       <c r="D828" t="n">
         <v>0.7747177890229662</v>
@@ -14527,7 +14527,7 @@
         <v>0.4888878735360589</v>
       </c>
       <c r="C830" t="n">
-        <v>0.5007090362929059</v>
+        <v>0.5007090362929058</v>
       </c>
       <c r="D830" t="n">
         <v>0.7752043596730245</v>
@@ -14694,7 +14694,7 @@
         <v>839</v>
       </c>
       <c r="B840" t="n">
-        <v>0.4883952293094304</v>
+        <v>0.4883952293094305</v>
       </c>
       <c r="C840" t="n">
         <v>0.5003520504501517</v>
@@ -14714,7 +14714,7 @@
         <v>0.4883460342028211</v>
       </c>
       <c r="C841" t="n">
-        <v>0.5003164596297478</v>
+        <v>0.5003164596297477</v>
       </c>
       <c r="D841" t="n">
         <v>0.7753016738030362</v>
@@ -14762,7 +14762,7 @@
         <v>843</v>
       </c>
       <c r="B844" t="n">
-        <v>0.4881985166871978</v>
+        <v>0.4881985166871979</v>
       </c>
       <c r="C844" t="n">
         <v>0.5002097998092326</v>
@@ -14864,7 +14864,7 @@
         <v>849</v>
       </c>
       <c r="B850" t="n">
-        <v>0.4879037632465337</v>
+        <v>0.4879037632465338</v>
       </c>
       <c r="C850" t="n">
         <v>0.4999969722707017</v>
@@ -14966,10 +14966,10 @@
         <v>855</v>
       </c>
       <c r="B856" t="n">
-        <v>0.4876093405232838</v>
+        <v>0.4876093405232839</v>
       </c>
       <c r="C856" t="n">
-        <v>0.4997847726092101</v>
+        <v>0.4997847726092102</v>
       </c>
       <c r="D856" t="n">
         <v>0.7754963020630595</v>
@@ -14983,7 +14983,7 @@
         <v>856</v>
       </c>
       <c r="B857" t="n">
-        <v>0.4875602986342594</v>
+        <v>0.4875602986342595</v>
       </c>
       <c r="C857" t="n">
         <v>0.499749464752188</v>
@@ -15000,7 +15000,7 @@
         <v>857</v>
       </c>
       <c r="B858" t="n">
-        <v>0.4875112643012023</v>
+        <v>0.4875112643012022</v>
       </c>
       <c r="C858" t="n">
         <v>0.4997141732902364</v>
@@ -15051,7 +15051,7 @@
         <v>860</v>
       </c>
       <c r="B861" t="n">
-        <v>0.4873642044348488</v>
+        <v>0.487364204434849</v>
       </c>
       <c r="C861" t="n">
         <v>0.4996083958312933</v>
@@ -15136,7 +15136,7 @@
         <v>865</v>
       </c>
       <c r="B866" t="n">
-        <v>0.4871192355401527</v>
+        <v>0.4871192355401528</v>
       </c>
       <c r="C866" t="n">
         <v>0.4994324145923939</v>
@@ -15187,7 +15187,7 @@
         <v>868</v>
       </c>
       <c r="B869" t="n">
-        <v>0.4869723235308933</v>
+        <v>0.4869723235308932</v>
       </c>
       <c r="C869" t="n">
         <v>0.4993270083449121</v>
@@ -15224,7 +15224,7 @@
         <v>0.4868744076815401</v>
       </c>
       <c r="C871" t="n">
-        <v>0.4992568112115156</v>
+        <v>0.4992568112115155</v>
       </c>
       <c r="D871" t="n">
         <v>0.7753989879330478</v>
@@ -15272,7 +15272,7 @@
         <v>873</v>
       </c>
       <c r="B874" t="n">
-        <v>0.4867275681537047</v>
+        <v>0.4867275681537046</v>
       </c>
       <c r="C874" t="n">
         <v>0.4991516232528375</v>
@@ -15323,7 +15323,7 @@
         <v>876</v>
       </c>
       <c r="B877" t="n">
-        <v>0.4865807650011976</v>
+        <v>0.4865807650011975</v>
       </c>
       <c r="C877" t="n">
         <v>0.4990465612090327</v>
@@ -15340,10 +15340,10 @@
         <v>877</v>
       </c>
       <c r="B878" t="n">
-        <v>0.4865318377907278</v>
+        <v>0.4865318377907279</v>
       </c>
       <c r="C878" t="n">
-        <v>0.4990115678501759</v>
+        <v>0.4990115678501758</v>
       </c>
       <c r="D878" t="n">
         <v>0.7758855585831063</v>
@@ -15377,7 +15377,7 @@
         <v>0.4864339929681629</v>
       </c>
       <c r="C880" t="n">
-        <v>0.4989416212647688</v>
+        <v>0.4989416212647687</v>
       </c>
       <c r="D880" t="n">
         <v>0.7758855585831063</v>
@@ -15411,7 +15411,7 @@
         <v>0.486336159656606</v>
       </c>
       <c r="C882" t="n">
-        <v>0.498871727237691</v>
+        <v>0.4988717272376912</v>
       </c>
       <c r="D882" t="n">
         <v>0.7758855585831063</v>
@@ -15459,7 +15459,7 @@
         <v>884</v>
       </c>
       <c r="B885" t="n">
-        <v>0.4861894278988744</v>
+        <v>0.4861894278988743</v>
       </c>
       <c r="C885" t="n">
         <v>0.4987669822295035</v>
@@ -15544,7 +15544,7 @@
         <v>889</v>
       </c>
       <c r="B890" t="n">
-        <v>0.485944910653642</v>
+        <v>0.4859449106536421</v>
       </c>
       <c r="C890" t="n">
         <v>0.4985926536127972</v>
@@ -15612,7 +15612,7 @@
         <v>893</v>
       </c>
       <c r="B894" t="n">
-        <v>0.4857493149688309</v>
+        <v>0.4857493149688308</v>
       </c>
       <c r="C894" t="n">
         <v>0.4984534018563546</v>
@@ -15714,7 +15714,7 @@
         <v>899</v>
       </c>
       <c r="B900" t="n">
-        <v>0.4854559219655627</v>
+        <v>0.4854559219655626</v>
       </c>
       <c r="C900" t="n">
         <v>0.4982448535407485</v>
@@ -15765,7 +15765,7 @@
         <v>902</v>
       </c>
       <c r="B903" t="n">
-        <v>0.4853092138626277</v>
+        <v>0.4853092138626275</v>
       </c>
       <c r="C903" t="n">
         <v>0.4981407185906859</v>
@@ -15802,7 +15802,7 @@
         <v>0.4852114003668627</v>
       </c>
       <c r="C905" t="n">
-        <v>0.4980713439859344</v>
+        <v>0.4980713439859343</v>
       </c>
       <c r="D905" t="n">
         <v>0.7763721292331647</v>
@@ -15853,7 +15853,7 @@
         <v>0.4850646637382115</v>
       </c>
       <c r="C908" t="n">
-        <v>0.4979673519519477</v>
+        <v>0.4979673519519479</v>
       </c>
       <c r="D908" t="n">
         <v>0.7763721292331647</v>
@@ -15870,7 +15870,7 @@
         <v>0.4850157462961855</v>
       </c>
       <c r="C909" t="n">
-        <v>0.4979327059337878</v>
+        <v>0.4979327059337877</v>
       </c>
       <c r="D909" t="n">
         <v>0.7764694433631764</v>
@@ -15884,7 +15884,7 @@
         <v>909</v>
       </c>
       <c r="B910" t="n">
-        <v>0.4849668258734456</v>
+        <v>0.4849668258734455</v>
       </c>
       <c r="C910" t="n">
         <v>0.4978980686438998</v>
@@ -15901,7 +15901,7 @@
         <v>910</v>
       </c>
       <c r="B911" t="n">
-        <v>0.4849179022487478</v>
+        <v>0.4849179022487479</v>
       </c>
       <c r="C911" t="n">
         <v>0.4978634399204099</v>
@@ -15952,7 +15952,7 @@
         <v>913</v>
       </c>
       <c r="B914" t="n">
-        <v>0.484771109924234</v>
+        <v>0.4847711099242339</v>
       </c>
       <c r="C914" t="n">
         <v>0.4977596035210711</v>
@@ -15986,7 +15986,7 @@
         <v>915</v>
       </c>
       <c r="B916" t="n">
-        <v>0.4846732282293763</v>
+        <v>0.4846732282293764</v>
       </c>
       <c r="C916" t="n">
         <v>0.497690419093986</v>
@@ -16040,7 +16040,7 @@
         <v>0.4845263708482715</v>
       </c>
       <c r="C919" t="n">
-        <v>0.497586698915173</v>
+        <v>0.4975866989151729</v>
       </c>
       <c r="D919" t="n">
         <v>0.7768586998832231</v>
@@ -16122,7 +16122,7 @@
         <v>923</v>
       </c>
       <c r="B924" t="n">
-        <v>0.4842814998431674</v>
+        <v>0.4842814998431675</v>
       </c>
       <c r="C924" t="n">
         <v>0.4974139714218485</v>
@@ -16156,7 +16156,7 @@
         <v>925</v>
       </c>
       <c r="B926" t="n">
-        <v>0.4841835077370102</v>
+        <v>0.4841835077370101</v>
       </c>
       <c r="C926" t="n">
         <v>0.4973449253259777</v>
@@ -16207,10 +16207,10 @@
         <v>928</v>
       </c>
       <c r="B929" t="n">
-        <v>0.4840364665429811</v>
+        <v>0.484036466542981</v>
       </c>
       <c r="C929" t="n">
-        <v>0.4972414000649324</v>
+        <v>0.4972414000649325</v>
       </c>
       <c r="D929" t="n">
         <v>0.7773452705332814</v>
@@ -16227,7 +16227,7 @@
         <v>0.4839874376561383</v>
       </c>
       <c r="C930" t="n">
-        <v>0.497206902666362</v>
+        <v>0.4972069026663619</v>
       </c>
       <c r="D930" t="n">
         <v>0.7773452705332814</v>
@@ -16258,7 +16258,7 @@
         <v>931</v>
       </c>
       <c r="B932" t="n">
-        <v>0.4838893556092639</v>
+        <v>0.483889355609264</v>
       </c>
       <c r="C932" t="n">
         <v>0.4971379233771884</v>
@@ -16275,7 +16275,7 @@
         <v>932</v>
       </c>
       <c r="B933" t="n">
-        <v>0.4838403019300647</v>
+        <v>0.4838403019300648</v>
       </c>
       <c r="C933" t="n">
         <v>0.4971034411438149</v>
@@ -16343,7 +16343,7 @@
         <v>936</v>
       </c>
       <c r="B937" t="n">
-        <v>0.4836439967094742</v>
+        <v>0.4836439967094741</v>
       </c>
       <c r="C937" t="n">
         <v>0.4969655576037894</v>
@@ -16360,7 +16360,7 @@
         <v>937</v>
       </c>
       <c r="B938" t="n">
-        <v>0.4835948964488641</v>
+        <v>0.483594896448864</v>
       </c>
       <c r="C938" t="n">
         <v>0.4969310972035614</v>
@@ -16414,7 +16414,7 @@
         <v>0.4834475338665167</v>
       </c>
       <c r="C941" t="n">
-        <v>0.4968277383909283</v>
+        <v>0.4968277383909281</v>
       </c>
       <c r="D941" t="n">
         <v>0.7777345270533281</v>
@@ -16445,10 +16445,10 @@
         <v>942</v>
       </c>
       <c r="B943" t="n">
-        <v>0.4833492379177812</v>
+        <v>0.4833492379177811</v>
       </c>
       <c r="C943" t="n">
-        <v>0.496758849429482</v>
+        <v>0.4967588494294821</v>
       </c>
       <c r="D943" t="n">
         <v>0.7777345270533281</v>
@@ -16462,7 +16462,7 @@
         <v>943</v>
       </c>
       <c r="B944" t="n">
-        <v>0.4833000728504609</v>
+        <v>0.4833000728504611</v>
       </c>
       <c r="C944" t="n">
         <v>0.4967244094981049</v>
@@ -16479,7 +16479,7 @@
         <v>944</v>
       </c>
       <c r="B945" t="n">
-        <v>0.483250896018416</v>
+        <v>0.4832508960184159</v>
       </c>
       <c r="C945" t="n">
         <v>0.4966899723655646</v>
@@ -16499,7 +16499,7 @@
         <v>0.4832017071431485</v>
       </c>
       <c r="C946" t="n">
-        <v>0.4966555378558486</v>
+        <v>0.4966555378558485</v>
       </c>
       <c r="D946" t="n">
         <v>0.7777345270533281</v>
@@ -16564,7 +16564,7 @@
         <v>949</v>
       </c>
       <c r="B950" t="n">
-        <v>0.4830048256029535</v>
+        <v>0.4830048256029536</v>
       </c>
       <c r="C950" t="n">
         <v>0.4965178225111307</v>
@@ -16581,7 +16581,7 @@
         <v>950</v>
       </c>
       <c r="B951" t="n">
-        <v>0.4829555722978732</v>
+        <v>0.4829555722978731</v>
       </c>
       <c r="C951" t="n">
         <v>0.4964833984613153</v>
@@ -16618,7 +16618,7 @@
         <v>0.4828570241970052</v>
       </c>
       <c r="C953" t="n">
-        <v>0.4964145548570459</v>
+        <v>0.4964145548570458</v>
       </c>
       <c r="D953" t="n">
         <v>0.7777345270533281</v>
@@ -16717,10 +16717,10 @@
         <v>958</v>
       </c>
       <c r="B959" t="n">
-        <v>0.4825610273642407</v>
+        <v>0.4825610273642406</v>
       </c>
       <c r="C959" t="n">
-        <v>0.4962080470512566</v>
+        <v>0.4962080470512565</v>
       </c>
       <c r="D959" t="n">
         <v>0.7777345270533281</v>
@@ -16737,7 +16737,7 @@
         <v>0.4825116401283511</v>
       </c>
       <c r="C960" t="n">
-        <v>0.4961736305347582</v>
+        <v>0.496173630534758</v>
       </c>
       <c r="D960" t="n">
         <v>0.7777345270533281</v>
@@ -16768,7 +16768,7 @@
         <v>961</v>
       </c>
       <c r="B962" t="n">
-        <v>0.4824128164028684</v>
+        <v>0.4824128164028683</v>
       </c>
       <c r="C962" t="n">
         <v>0.4961047970982471</v>
@@ -16802,10 +16802,10 @@
         <v>963</v>
       </c>
       <c r="B964" t="n">
-        <v>0.4823139250754664</v>
+        <v>0.4823139250754663</v>
       </c>
       <c r="C964" t="n">
-        <v>0.4960359618908315</v>
+        <v>0.4960359618908316</v>
       </c>
       <c r="D964" t="n">
         <v>0.7777345270533281</v>
@@ -16819,7 +16819,7 @@
         <v>964</v>
       </c>
       <c r="B965" t="n">
-        <v>0.4822644533366746</v>
+        <v>0.4822644533366744</v>
       </c>
       <c r="C965" t="n">
         <v>0.4960015431578499</v>
@@ -16853,7 +16853,7 @@
         <v>966</v>
       </c>
       <c r="B967" t="n">
-        <v>0.4821654562598394</v>
+        <v>0.4821654562598393</v>
       </c>
       <c r="C967" t="n">
         <v>0.4959327024958637</v>
@@ -16890,7 +16890,7 @@
         <v>0.4820663857860815</v>
       </c>
       <c r="C969" t="n">
-        <v>0.495863856312363</v>
+        <v>0.4958638563123629</v>
       </c>
       <c r="D969" t="n">
         <v>0.7776372129233164</v>
@@ -16921,10 +16921,10 @@
         <v>970</v>
       </c>
       <c r="B971" t="n">
-        <v>0.4819672396004414</v>
+        <v>0.4819672396004413</v>
       </c>
       <c r="C971" t="n">
-        <v>0.4957950030820564</v>
+        <v>0.4957950030820565</v>
       </c>
       <c r="D971" t="n">
         <v>0.7776372129233164</v>
@@ -16958,7 +16958,7 @@
         <v>0.4818680153926247</v>
       </c>
       <c r="C973" t="n">
-        <v>0.4957261412636069</v>
+        <v>0.4957261412636068</v>
       </c>
       <c r="D973" t="n">
         <v>0.7776372129233164</v>
@@ -16972,7 +16972,7 @@
         <v>973</v>
       </c>
       <c r="B974" t="n">
-        <v>0.4818183733101898</v>
+        <v>0.4818183733101897</v>
       </c>
       <c r="C974" t="n">
         <v>0.4956917066474728</v>
@@ -17057,7 +17057,7 @@
         <v>978</v>
       </c>
       <c r="B979" t="n">
-        <v>0.4815698516441</v>
+        <v>0.4815698516441001</v>
       </c>
       <c r="C979" t="n">
         <v>0.4955194885993444</v>
@@ -17108,10 +17108,10 @@
         <v>981</v>
       </c>
       <c r="B982" t="n">
-        <v>0.4814204793891968</v>
+        <v>0.4814204793891969</v>
       </c>
       <c r="C982" t="n">
-        <v>0.4954161145618777</v>
+        <v>0.4954161145618778</v>
       </c>
       <c r="D982" t="n">
         <v>0.7782210977033865</v>
@@ -17125,7 +17125,7 @@
         <v>982</v>
       </c>
       <c r="B983" t="n">
-        <v>0.4813706437323644</v>
+        <v>0.4813706437323645</v>
       </c>
       <c r="C983" t="n">
         <v>0.4953816481215625</v>
@@ -17145,7 +17145,7 @@
         <v>0.4813207851558889</v>
       </c>
       <c r="C984" t="n">
-        <v>0.4953471771205458</v>
+        <v>0.4953471771205457</v>
       </c>
       <c r="D984" t="n">
         <v>0.7782210977033865</v>
@@ -17176,7 +17176,7 @@
         <v>985</v>
       </c>
       <c r="B986" t="n">
-        <v>0.4812209981308959</v>
+        <v>0.4812209981308957</v>
       </c>
       <c r="C986" t="n">
         <v>0.4952782205930978</v>
@@ -17244,7 +17244,7 @@
         <v>989</v>
       </c>
       <c r="B990" t="n">
-        <v>0.4810211368702081</v>
+        <v>0.481021136870208</v>
       </c>
       <c r="C990" t="n">
         <v>0.4951402434398327</v>
@@ -17278,7 +17278,7 @@
         <v>991</v>
       </c>
       <c r="B992" t="n">
-        <v>0.4809210582700707</v>
+        <v>0.4809210582700706</v>
       </c>
       <c r="C992" t="n">
         <v>0.4950712193240352</v>
@@ -17349,7 +17349,7 @@
         <v>0.480720594396927</v>
       </c>
       <c r="C996" t="n">
-        <v>0.4949330910646755</v>
+        <v>0.4949330910646756</v>
       </c>
       <c r="D996" t="n">
         <v>0.7786103542234333</v>
@@ -17363,10 +17363,10 @@
         <v>996</v>
       </c>
       <c r="B997" t="n">
-        <v>0.4806704129990608</v>
+        <v>0.4806704129990609</v>
       </c>
       <c r="C997" t="n">
-        <v>0.4948985409904719</v>
+        <v>0.494898540990472</v>
       </c>
       <c r="D997" t="n">
         <v>0.7786103542234333</v>
@@ -17417,7 +17417,7 @@
         <v>0.4805197076219507</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.4947948437945344</v>
+        <v>0.4947948437945345</v>
       </c>
       <c r="D1000" t="n">
         <v>0.778707668353445</v>
